--- a/results_cv.xlsx
+++ b/results_cv.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4616666666666667</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5258333333333334</v>
+        <v>0.4258333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3708333333333333</v>
+        <v>0.3741666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.3341666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3758333333333333</v>
+        <v>0.2816666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>0.5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3041666666666666</v>
+        <v>0.3091666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3216666666666667</v>
+        <v>0.3225</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3741666666666666</v>
+        <v>0.3341666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2441666666666666</v>
+        <v>0.3358333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>0.9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.45</v>
+        <v>0.3483333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1941666666666667</v>
+        <v>0.3991666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>1.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2525</v>
+        <v>0.3366666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>1.2</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2566666666666667</v>
+        <v>0.2983333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>1.3</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3433333333333333</v>
+        <v>0.4008333333333334</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>1.4</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3591666666666666</v>
+        <v>0.3241666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>1.5</v>
       </c>
       <c r="B17" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>1.6</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3975</v>
+        <v>0.3075</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>1.7</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3675</v>
+        <v>0.3108333333333334</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>1.8</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3191666666666667</v>
+        <v>0.3216666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>1.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2183333333333333</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>0.295</v>
+        <v>0.3075</v>
       </c>
     </row>
   </sheetData>
